--- a/05. Res/modelos/particion_train_test_por_id.xlsx
+++ b/05. Res/modelos/particion_train_test_por_id.xlsx
@@ -390,13 +390,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>84343</v>
+        <v>84255</v>
       </c>
       <c r="C2" t="n">
         <v>42796</v>
       </c>
       <c r="D2" t="n">
-        <v>0.799277889390091</v>
+        <v>0.798443955877336</v>
       </c>
     </row>
     <row r="3">
@@ -404,13 +404,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>21181</v>
+        <v>21269</v>
       </c>
       <c r="C3" t="n">
         <v>10699</v>
       </c>
       <c r="D3" t="n">
-        <v>0.200722110609909</v>
+        <v>0.201556044122664</v>
       </c>
     </row>
   </sheetData>
